--- a/report.xlsx
+++ b/report.xlsx
@@ -15,35 +15,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="27">
   <si>
     <t>0</t>
   </si>
   <si>
+    <t>sdfsdfsdfsd</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Item:</t>
+  </si>
+  <si>
+    <t>Info:</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>INS_CERT</t>
+  </si>
+  <si>
+    <t>Missing</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>sdfsdfsdfsd</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Item:</t>
-  </si>
-  <si>
-    <t>Info:</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>INS_CERT</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
     <t>IFTA_LICENSE</t>
   </si>
   <si>
@@ -62,6 +62,9 @@
     <t>asdas</t>
   </si>
   <si>
+    <t>No Driver Files</t>
+  </si>
+  <si>
     <t>Driver Name:</t>
   </si>
   <si>
@@ -89,10 +92,10 @@
     <t>PEV</t>
   </si>
   <si>
-    <t>Truck Name:</t>
-  </si>
-  <si>
-    <t>Trailer Name:</t>
+    <t>No Truck Files</t>
+  </si>
+  <si>
+    <t>No Trailer Files</t>
   </si>
 </sst>
 </file>
@@ -347,13 +350,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
@@ -380,52 +386,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="2" max="2" width="23.4375" customWidth="true"/>
-    <col min="3" max="3" width="31.25" customWidth="true"/>
+    <col min="2" max="2" width="31.25" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="5">
         <v>2</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" t="s" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="4">
+      <c r="B2" t="s" s="5">
         <v>3</v>
       </c>
-      <c r="B2" t="s" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s" s="4">
+      <c r="C2" t="s" s="5">
         <v>4</v>
       </c>
-      <c r="D2" t="s" s="4">
+      <c r="D2" t="s" s="5">
         <v>5</v>
       </c>
-      <c r="E2" t="s" s="4">
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>1</v>
-      </c>
       <c r="C3" t="s" s="2">
         <v>7</v>
       </c>
@@ -434,56 +431,56 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n" s="2">
+      <c r="A4" t="n" s="6">
         <v>2.0</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n" s="2">
+      <c r="A5" t="n" s="6">
         <v>3.0</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n" s="2">
+      <c r="A6" t="n" s="6">
         <v>4.0</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n" s="2">
+      <c r="A7" t="n" s="6">
         <v>5.0</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>8</v>
@@ -493,41 +490,33 @@
       <c r="A10" t="s" s="3">
         <v>13</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s" s="3">
+      <c r="B10" t="s" s="3">
         <v>14</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" t="s" s="2">
-        <v>1</v>
-      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="4">
+      <c r="A11" t="s" s="5">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s" s="5">
         <v>3</v>
       </c>
-      <c r="B11" t="s" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s" s="4">
+      <c r="C11" t="s" s="5">
         <v>4</v>
       </c>
-      <c r="D11" t="s" s="4">
+      <c r="D11" t="s" s="5">
         <v>5</v>
       </c>
-      <c r="E11" t="s" s="4">
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>1</v>
-      </c>
       <c r="C12" t="s" s="2">
         <v>7</v>
       </c>
@@ -536,56 +525,56 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n" s="2">
+      <c r="A13" t="n" s="6">
         <v>2.0</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n" s="2">
+      <c r="A14" t="n" s="6">
         <v>3.0</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n" s="2">
+      <c r="A15" t="n" s="6">
         <v>4.0</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n" s="2">
+      <c r="A16" t="n" s="6">
         <v>5.0</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>8</v>
@@ -593,8 +582,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B10:D10"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -610,269 +599,296 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="2">
+      <c r="A1" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
-        <v>2</v>
-      </c>
+      <c r="C1" s="8"/>
       <c r="D1" s="8"/>
-      <c r="E1" t="s" s="2">
-        <v>1</v>
-      </c>
+      <c r="E1" s="9"/>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
+        <v>15</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="3">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s" s="5">
         <v>3</v>
       </c>
-      <c r="B2" t="s" s="4">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s" s="4">
+      <c r="D6" t="s" s="5">
         <v>4</v>
       </c>
-      <c r="D2" t="s" s="4">
+      <c r="E6" t="s" s="5">
         <v>5</v>
       </c>
-      <c r="E2" t="s" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" t="s" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s" s="4">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s" s="4">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s" s="4">
-        <v>6</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n" s="2">
+      <c r="A7" t="n" s="6">
         <v>1.0</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n" s="2">
+      <c r="A8" t="n" s="6">
         <v>2.0</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n" s="2">
+      <c r="D14" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="6">
         <v>3.0</v>
       </c>
-      <c r="B9" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n" s="2">
+      <c r="B16" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="6">
         <v>4.0</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n" s="2">
+      <c r="B17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="6">
         <v>5.0</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n" s="2">
+      <c r="B18" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="6">
         <v>6.0</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n" s="2">
+      <c r="B19" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="6">
         <v>7.0</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n" s="2">
-        <v>7.0</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C5:D5"/>
+  <mergeCells count="3">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -891,70 +907,48 @@
       <c r="A1" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
-        <v>2</v>
-      </c>
+      <c r="C1" s="8"/>
       <c r="D1" s="8"/>
-      <c r="E1" t="s" s="2">
-        <v>1</v>
-      </c>
+      <c r="E1" s="9"/>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s" s="4">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s" s="4">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s" s="4">
-        <v>6</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="3">
         <v>13</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s" s="3">
+      <c r="B5" t="s" s="3">
         <v>14</v>
       </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" t="s" s="2">
-        <v>1</v>
-      </c>
+      <c r="E5" s="9"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s" s="4">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s" s="4">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s" s="4">
-        <v>6</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C5:D5"/>
+  <mergeCells count="4">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -973,70 +967,48 @@
       <c r="A1" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
-        <v>2</v>
-      </c>
+      <c r="C1" s="8"/>
       <c r="D1" s="8"/>
-      <c r="E1" t="s" s="2">
-        <v>1</v>
-      </c>
+      <c r="E1" s="9"/>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s" s="4">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s" s="4">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s" s="4">
-        <v>6</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="3">
         <v>13</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s" s="3">
+      <c r="B5" t="s" s="3">
         <v>14</v>
       </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" t="s" s="2">
-        <v>1</v>
-      </c>
+      <c r="E5" s="9"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s" s="4">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s" s="4">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s" s="4">
-        <v>6</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C5:D5"/>
+  <mergeCells count="4">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
